--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="365">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-18T09:05:02+00:00</t>
+    <t>2025-04-24T12:12:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -569,10 +569,7 @@
     <t>A classification of the type of consents found in the statement. This element supports indexing and retrieval of consent statements.</t>
   </si>
   <si>
-    <t>A classification of the type of consents found in a consent statement.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-category</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/consent-category-value-set</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -590,7 +587,7 @@
     <t>Consent.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
 </t>
   </si>
   <si>
@@ -1055,6 +1052,31 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/consent-content-code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:coding.code}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Consent.provision.code:alimentationDmp</t>
+  </si>
+  <si>
+    <t>alimentationDmp</t>
+  </si>
+  <si>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/dmp-feed-consent-status-vs</t>
+  </si>
+  <si>
+    <t>Consent.provision.code:consultationDmp</t>
+  </si>
+  <si>
+    <t>consultationDmp</t>
+  </si>
+  <si>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/dmp-access-consent-status-vs</t>
   </si>
   <si>
     <t>Consent.provision.dataPeriod</t>
@@ -1434,12 +1456,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN58"/>
+  <dimension ref="A1:AN60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="34.33203125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="34.33203125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1462,7 +1484,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="107.984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="45.0703125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="57.8046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -2984,7 +3006,7 @@
         <v>90</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>78</v>
@@ -3029,13 +3051,11 @@
         <v>78</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="Y14" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="Y14" s="2"/>
+      <c r="Z14" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>78</v>
@@ -3068,24 +3088,24 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>183</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3093,7 +3113,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>90</v>
@@ -3108,16 +3128,16 @@
         <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3167,7 +3187,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3182,24 +3202,24 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="AL15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>191</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3207,7 +3227,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>90</v>
@@ -3222,16 +3242,16 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3281,7 +3301,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3296,28 +3316,28 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AM16" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>200</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3336,16 +3356,16 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3395,7 +3415,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3410,28 +3430,28 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>209</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3450,13 +3470,13 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3507,7 +3527,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3522,7 +3542,7 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>78</v>
@@ -3531,15 +3551,15 @@
         <v>78</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3562,16 +3582,16 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3621,7 +3641,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3639,7 +3659,7 @@
         <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>78</v>
@@ -3650,10 +3670,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3676,13 +3696,13 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3733,7 +3753,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3762,10 +3782,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3788,13 +3808,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3845,7 +3865,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3866,7 +3886,7 @@
         <v>78</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>78</v>
@@ -3874,10 +3894,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3906,7 +3926,7 @@
         <v>137</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>139</v>
@@ -3959,7 +3979,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3980,7 +4000,7 @@
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
@@ -3988,14 +4008,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4017,10 +4037,10 @@
         <v>136</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>139</v>
@@ -4075,7 +4095,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4104,10 +4124,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4133,10 +4153,10 @@
         <v>104</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4187,7 +4207,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4196,7 +4216,7 @@
         <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>102</v>
@@ -4216,10 +4236,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4245,13 +4265,13 @@
         <v>104</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4301,7 +4321,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4310,7 +4330,7 @@
         <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>102</v>
@@ -4330,10 +4350,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4359,16 +4379,16 @@
         <v>169</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -4396,11 +4416,11 @@
         <v>172</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>253</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
       </c>
@@ -4417,7 +4437,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4426,7 +4446,7 @@
         <v>90</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>102</v>
@@ -4446,10 +4466,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4472,13 +4492,13 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4529,7 +4549,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4558,10 +4578,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4584,13 +4604,13 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4641,7 +4661,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4662,7 +4682,7 @@
         <v>78</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -4670,10 +4690,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4702,7 +4722,7 @@
         <v>137</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>139</v>
@@ -4755,7 +4775,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4776,7 +4796,7 @@
         <v>78</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -4784,14 +4804,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4813,10 +4833,10 @@
         <v>136</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>139</v>
@@ -4871,7 +4891,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -4900,10 +4920,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4926,13 +4946,13 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4983,7 +5003,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>90</v>
@@ -5012,10 +5032,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5038,13 +5058,13 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5095,7 +5115,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5124,10 +5144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5150,13 +5170,13 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5207,7 +5227,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5236,10 +5256,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5262,13 +5282,13 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5319,7 +5339,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5348,10 +5368,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5374,13 +5394,13 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5431,7 +5451,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5452,7 +5472,7 @@
         <v>78</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
@@ -5460,10 +5480,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5492,7 +5512,7 @@
         <v>137</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>139</v>
@@ -5545,7 +5565,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5566,7 +5586,7 @@
         <v>78</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -5574,14 +5594,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5603,10 +5623,10 @@
         <v>136</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>139</v>
@@ -5661,7 +5681,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5690,10 +5710,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5719,10 +5739,10 @@
         <v>110</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5752,11 +5772,11 @@
         <v>161</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="Z38" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>281</v>
-      </c>
       <c r="AA38" t="s" s="2">
         <v>78</v>
       </c>
@@ -5773,7 +5793,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5802,10 +5822,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5828,13 +5848,13 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5885,7 +5905,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -5914,10 +5934,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5940,13 +5960,13 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5954,7 +5974,7 @@
         <v>78</v>
       </c>
       <c r="Q40" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="R40" t="s" s="2">
         <v>78</v>
@@ -5999,7 +6019,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6028,10 +6048,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6054,13 +6074,13 @@
         <v>78</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6111,7 +6131,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6132,7 +6152,7 @@
         <v>78</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>78</v>
@@ -6140,10 +6160,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6172,7 +6192,7 @@
         <v>137</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>139</v>
@@ -6225,7 +6245,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6246,7 +6266,7 @@
         <v>78</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>78</v>
@@ -6254,14 +6274,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6283,10 +6303,10 @@
         <v>136</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>139</v>
@@ -6341,7 +6361,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6370,10 +6390,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6399,10 +6419,10 @@
         <v>169</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6432,11 +6452,11 @@
         <v>172</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="Z44" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="Z44" t="s" s="2">
-        <v>297</v>
-      </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
       </c>
@@ -6453,7 +6473,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>90</v>
@@ -6482,10 +6502,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6508,13 +6528,13 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6565,7 +6585,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>90</v>
@@ -6594,10 +6614,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6623,48 +6643,48 @@
         <v>169</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q46" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="R46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X46" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="R46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X46" t="s" s="2">
+      <c r="Y46" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="Y46" t="s" s="2">
+      <c r="Z46" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="Z46" t="s" s="2">
-        <v>309</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>78</v>
       </c>
@@ -6681,7 +6701,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6710,10 +6730,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6736,16 +6756,16 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6774,11 +6794,11 @@
         <v>172</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>316</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>78</v>
       </c>
@@ -6795,7 +6815,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -6824,10 +6844,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6850,16 +6870,16 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6888,11 +6908,11 @@
         <v>172</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>322</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>78</v>
       </c>
@@ -6909,7 +6929,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -6938,10 +6958,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6964,16 +6984,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7002,11 +7022,11 @@
         <v>172</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="Z49" t="s" s="2">
-        <v>328</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>78</v>
       </c>
@@ -7023,7 +7043,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7052,10 +7072,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7081,13 +7101,13 @@
         <v>169</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7113,31 +7133,29 @@
         <v>78</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="Z50" t="s" s="2">
+      <c r="AA50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB50" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AA50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>78</v>
-      </c>
+      <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>78</v>
+        <v>335</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7166,12 +7184,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="D51" t="s" s="2">
         <v>78</v>
       </c>
@@ -7192,16 +7212,16 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>283</v>
+        <v>169</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7227,13 +7247,11 @@
         <v>78</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>78</v>
+        <v>338</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>78</v>
@@ -7251,13 +7269,13 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>78</v>
@@ -7283,9 +7301,11 @@
         <v>339</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="D52" t="s" s="2">
         <v>78</v>
       </c>
@@ -7294,7 +7314,7 @@
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>78</v>
@@ -7306,22 +7326,22 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>223</v>
+        <v>169</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q52" t="s" s="2">
-        <v>342</v>
-      </c>
+      <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
         <v>78</v>
       </c>
@@ -7341,13 +7361,11 @@
         <v>78</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>78</v>
+        <v>341</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>78</v>
@@ -7365,7 +7383,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7386,7 +7404,7 @@
         <v>78</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -7394,10 +7412,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7417,18 +7435,20 @@
         <v>78</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>227</v>
+        <v>282</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>228</v>
+        <v>343</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -7477,7 +7497,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>230</v>
+        <v>342</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7489,7 +7509,7 @@
         <v>78</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>78</v>
@@ -7498,7 +7518,7 @@
         <v>78</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>231</v>
+        <v>78</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -7506,14 +7526,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7529,25 +7549,25 @@
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>136</v>
+        <v>222</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>137</v>
+        <v>347</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q54" s="2"/>
+      <c r="Q54" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="R54" t="s" s="2">
         <v>78</v>
       </c>
@@ -7591,7 +7611,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>234</v>
+        <v>346</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7603,7 +7623,7 @@
         <v>78</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>78</v>
@@ -7612,7 +7632,7 @@
         <v>78</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>231</v>
+        <v>189</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>78</v>
@@ -7620,46 +7640,42 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>136</v>
+        <v>226</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>78</v>
       </c>
@@ -7707,19 +7723,19 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>78</v>
@@ -7728,7 +7744,7 @@
         <v>78</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>133</v>
+        <v>230</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -7736,21 +7752,21 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>78</v>
@@ -7759,18 +7775,20 @@
         <v>78</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>347</v>
+        <v>137</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -7795,13 +7813,13 @@
         <v>78</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>349</v>
+        <v>78</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>350</v>
+        <v>78</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>78</v>
@@ -7819,19 +7837,19 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>346</v>
+        <v>233</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>78</v>
@@ -7840,7 +7858,7 @@
         <v>78</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>78</v>
+        <v>230</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -7848,42 +7866,46 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>78</v>
+        <v>235</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J57" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>352</v>
+        <v>136</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>353</v>
+        <v>236</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
       </c>
@@ -7931,19 +7953,19 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>351</v>
+        <v>238</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>78</v>
@@ -7952,7 +7974,7 @@
         <v>78</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -7960,10 +7982,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7971,10 +7993,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>78</v>
@@ -7983,16 +8005,16 @@
         <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8019,13 +8041,13 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>78</v>
+        <v>356</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>78</v>
+        <v>357</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -8043,13 +8065,13 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>78</v>
@@ -8067,6 +8089,230 @@
         <v>78</v>
       </c>
       <c r="AN58" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>78</v>
       </c>
     </row>

--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:12:45+00:00</t>
+    <t>2025-04-24T12:14:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:14:49+00:00</t>
+    <t>2025-04-24T12:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:53:37+00:00</t>
+    <t>2025-04-25T09:56:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -587,7 +587,7 @@
     <t>Consent.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-ins)
 </t>
   </si>
   <si>

--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-consent-fr</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-consent-fr</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T09:56:34+00:00</t>
+    <t>2025-04-25T14:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -569,7 +569,7 @@
     <t>A classification of the type of consents found in the statement. This element supports indexing and retrieval of consent statements.</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/consent-category-value-set</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/ValueSet/consent-category-value-set</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1067,7 +1067,7 @@
     <t>alimentationDmp</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/dmp-feed-consent-status-vs</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/ValueSet/dmp-feed-consent-status-vs</t>
   </si>
   <si>
     <t>Consent.provision.code:consultationDmp</t>
@@ -1076,7 +1076,7 @@
     <t>consultationDmp</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/dmp-access-consent-status-vs</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/ValueSet/dmp-access-consent-status-vs</t>
   </si>
   <si>
     <t>Consent.provision.dataPeriod</t>
@@ -1484,7 +1484,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="107.984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="57.8046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="77.546875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T14:29:23+00:00</t>
+    <t>2025-04-25T16:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -587,7 +587,7 @@
     <t>Consent.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-ins)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
 </t>
   </si>
   <si>

--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-consent-fr</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-consent-fr</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T16:50:14+00:00</t>
+    <t>2025-04-28T06:55:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -569,7 +569,7 @@
     <t>A classification of the type of consents found in the statement. This element supports indexing and retrieval of consent statements.</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/ValueSet/consent-category-value-set</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/consent-category-value-set</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1067,7 +1067,7 @@
     <t>alimentationDmp</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/ValueSet/dmp-feed-consent-status-vs</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/dmp-feed-consent-status-vs</t>
   </si>
   <si>
     <t>Consent.provision.code:consultationDmp</t>
@@ -1076,7 +1076,7 @@
     <t>consultationDmp</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/ValueSet/dmp-access-consent-status-vs</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/dmp-access-consent-status-vs</t>
   </si>
   <si>
     <t>Consent.provision.dataPeriod</t>
@@ -1484,7 +1484,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="107.984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="77.546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="57.8046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T06:55:35+00:00</t>
+    <t>2025-04-28T10:41:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="364">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T10:41:02+00:00</t>
+    <t>2025-05-05T08:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1067,16 +1067,13 @@
     <t>alimentationDmp</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/dmp-feed-consent-status-vs</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/preadmission-consent-value-set</t>
   </si>
   <si>
     <t>Consent.provision.code:consultationDmp</t>
   </si>
   <si>
     <t>consultationDmp</t>
-  </si>
-  <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/dmp-access-consent-status-vs</t>
   </si>
   <si>
     <t>Consent.provision.dataPeriod</t>
@@ -1484,7 +1481,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="107.984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="57.8046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.1015625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -7365,7 +7362,7 @@
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>78</v>
@@ -7412,10 +7409,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7441,13 +7438,13 @@
         <v>282</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7497,7 +7494,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7526,10 +7523,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7555,10 +7552,10 @@
         <v>222</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7566,7 +7563,7 @@
         <v>78</v>
       </c>
       <c r="Q54" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="R54" t="s" s="2">
         <v>78</v>
@@ -7611,7 +7608,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7640,10 +7637,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7752,10 +7749,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7866,10 +7863,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7982,10 +7979,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8011,10 +8008,10 @@
         <v>110</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8044,11 +8041,11 @@
         <v>161</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
       </c>
@@ -8065,7 +8062,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>90</v>
@@ -8094,10 +8091,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8120,13 +8117,13 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8177,7 +8174,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>90</v>
@@ -8206,10 +8203,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8235,10 +8232,10 @@
         <v>81</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8289,7 +8286,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>

--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-05T08:51:40+00:00</t>
+    <t>2025-05-06T13:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2971" uniqueCount="386">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T13:54:59+00:00</t>
+    <t>2025-05-14T09:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -517,6 +517,9 @@
     <t>The Consent Directive that is pointed to might be in various lifecycle states, e.g., a revoked Consent Directive.</t>
   </si>
   <si>
+    <t>active</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
@@ -551,6 +554,14 @@
     <t>A selector of the type of consent being presented: ADR, Privacy, Treatment, Research.  This list is now extensible.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/consentscope"/&gt;
+    &lt;code value="patient-privacy"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>extensible</t>
   </si>
   <si>
@@ -569,7 +580,18 @@
     <t>A classification of the type of consents found in the statement. This element supports indexing and retrieval of consent statements.</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/consent-category-value-set</t>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="59284-0"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>A classification of the type of consents found in a consent statement.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/consent-category</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -886,10 +908,7 @@
     <t>Action  to take - permit or deny - when the rule conditions are met.  Not permitted in root rule, required in all nested rules.</t>
   </si>
   <si>
-    <t>How a rule statement is applied, such as adding additional consent or removing consent.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-provision-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-provision-type</t>
   </si>
   <si>
     <t>Consent.provision.period</t>
@@ -1054,28 +1073,6 @@
     <t>http://hl7.org/fhir/ValueSet/consent-content-code</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.code}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Consent.provision.code:alimentationDmp</t>
-  </si>
-  <si>
-    <t>alimentationDmp</t>
-  </si>
-  <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/preadmission-consent-value-set</t>
-  </si>
-  <si>
-    <t>Consent.provision.code:consultationDmp</t>
-  </si>
-  <si>
-    <t>consultationDmp</t>
-  </si>
-  <si>
     <t>Consent.provision.dataPeriod</t>
   </si>
   <si>
@@ -1144,6 +1141,84 @@
   </si>
   <si>
     <t>Rules which provide exceptions to the base rule or subrules.</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision.id</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision.extension</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision.modifierExtension</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision.type</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision.period</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision.actor</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision.actor.id</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision.actor.extension</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision.actor.modifierExtension</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision.actor.role</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision.actor.reference</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision.action</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision.securityLabel</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision.purpose</t>
+  </si>
+  <si>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/preadmission-consent-purpose-reason-vs</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision.class</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision.code</t>
+  </si>
+  <si>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/preadmission-consent-code-value-set</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision.dataPeriod</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision.data</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision.data.id</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision.data.extension</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision.data.modifierExtension</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision.data.meaning</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision.data.reference</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision.provision</t>
   </si>
 </sst>
 </file>
@@ -1453,12 +1528,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN60"/>
+  <dimension ref="A1:AN82"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="34.33203125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="34.33203125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.5546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="42.015625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.015625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1481,7 +1556,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="107.984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.1015625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.4609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -2806,7 +2881,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>78</v>
@@ -2824,13 +2899,13 @@
         <v>78</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>78</v>
@@ -2863,24 +2938,24 @@
         <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2903,13 +2978,13 @@
         <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2921,7 +2996,7 @@
         <v>78</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>78</v>
@@ -2936,13 +3011,13 @@
         <v>78</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>78</v>
@@ -2960,7 +3035,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>90</v>
@@ -2989,10 +3064,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3003,7 +3078,7 @@
         <v>90</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>78</v>
@@ -3015,13 +3090,13 @@
         <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3033,7 +3108,7 @@
         <v>78</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>78</v>
@@ -3048,11 +3123,13 @@
         <v>78</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>78</v>
@@ -3070,7 +3147,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>90</v>
@@ -3085,24 +3162,24 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3125,16 +3202,16 @@
         <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3184,7 +3261,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3199,24 +3276,24 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3239,16 +3316,16 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3298,7 +3375,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3313,28 +3390,28 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3353,16 +3430,16 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3412,7 +3489,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3427,28 +3504,28 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3467,13 +3544,13 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3524,7 +3601,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3539,7 +3616,7 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>78</v>
@@ -3548,15 +3625,15 @@
         <v>78</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3579,16 +3656,16 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3638,7 +3715,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3656,7 +3733,7 @@
         <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>78</v>
@@ -3667,10 +3744,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3693,13 +3770,13 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3750,7 +3827,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3779,10 +3856,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3805,13 +3882,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3862,7 +3939,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3883,7 +3960,7 @@
         <v>78</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>78</v>
@@ -3891,10 +3968,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3923,7 +4000,7 @@
         <v>137</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>139</v>
@@ -3976,7 +4053,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3997,7 +4074,7 @@
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
@@ -4005,14 +4082,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4034,10 +4111,10 @@
         <v>136</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>139</v>
@@ -4092,7 +4169,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4121,10 +4198,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4150,10 +4227,10 @@
         <v>104</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4204,7 +4281,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4213,7 +4290,7 @@
         <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>102</v>
@@ -4233,10 +4310,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4262,13 +4339,13 @@
         <v>104</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4318,7 +4395,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4327,7 +4404,7 @@
         <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>102</v>
@@ -4347,10 +4424,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4373,19 +4450,19 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -4410,13 +4487,13 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
@@ -4434,16 +4511,16 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI26" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>102</v>
@@ -4463,10 +4540,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4489,13 +4566,13 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4546,7 +4623,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4575,10 +4652,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4601,13 +4678,13 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4658,7 +4735,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4679,7 +4756,7 @@
         <v>78</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -4687,10 +4764,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4719,7 +4796,7 @@
         <v>137</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>139</v>
@@ -4772,7 +4849,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4793,7 +4870,7 @@
         <v>78</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -4801,14 +4878,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4830,10 +4907,10 @@
         <v>136</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>139</v>
@@ -4888,7 +4965,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -4917,10 +4994,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4943,13 +5020,13 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5000,7 +5077,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>90</v>
@@ -5029,10 +5106,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5055,13 +5132,13 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5112,7 +5189,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5141,10 +5218,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5167,13 +5244,13 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5224,7 +5301,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5253,10 +5330,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5264,7 +5341,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>90</v>
@@ -5279,13 +5356,13 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5336,7 +5413,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5365,10 +5442,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5391,13 +5468,13 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5448,7 +5525,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5469,7 +5546,7 @@
         <v>78</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
@@ -5477,10 +5554,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5509,7 +5586,7 @@
         <v>137</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>139</v>
@@ -5562,7 +5639,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5583,7 +5660,7 @@
         <v>78</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -5591,14 +5668,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5620,10 +5697,10 @@
         <v>136</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>139</v>
@@ -5678,7 +5755,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5707,10 +5784,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5718,7 +5795,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>90</v>
@@ -5736,10 +5813,10 @@
         <v>110</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5766,31 +5843,29 @@
         <v>78</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5819,10 +5894,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5845,13 +5920,13 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5902,7 +5977,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -5931,10 +6006,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5957,13 +6032,13 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5971,52 +6046,52 @@
         <v>78</v>
       </c>
       <c r="Q40" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="R40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="R40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6045,10 +6120,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6071,13 +6146,13 @@
         <v>78</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6128,7 +6203,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6149,7 +6224,7 @@
         <v>78</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>78</v>
@@ -6157,10 +6232,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6189,7 +6264,7 @@
         <v>137</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>139</v>
@@ -6242,7 +6317,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6263,7 +6338,7 @@
         <v>78</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>78</v>
@@ -6271,14 +6346,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6300,10 +6375,10 @@
         <v>136</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>139</v>
@@ -6358,7 +6433,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6387,10 +6462,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6413,13 +6488,13 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6446,31 +6521,31 @@
         <v>78</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>90</v>
@@ -6499,10 +6574,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6525,13 +6600,13 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6582,7 +6657,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>90</v>
@@ -6611,10 +6686,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6637,23 +6712,23 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q46" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="R46" t="s" s="2">
         <v>78</v>
@@ -6674,13 +6749,13 @@
         <v>78</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>78</v>
@@ -6698,7 +6773,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6727,10 +6802,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6753,16 +6828,16 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6788,13 +6863,13 @@
         <v>78</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>78</v>
@@ -6812,7 +6887,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -6841,10 +6916,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6867,16 +6942,16 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6902,13 +6977,13 @@
         <v>78</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>78</v>
@@ -6926,7 +7001,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -6955,10 +7030,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6981,16 +7056,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7016,13 +7091,13 @@
         <v>78</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>78</v>
@@ -7040,7 +7115,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7069,10 +7144,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7095,16 +7170,16 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7130,29 +7205,31 @@
         <v>78</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AC50" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>335</v>
+        <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7181,14 +7258,12 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="C51" t="s" s="2">
         <v>337</v>
       </c>
+      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>78</v>
       </c>
@@ -7209,16 +7284,16 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>169</v>
+        <v>285</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7244,11 +7319,13 @@
         <v>78</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>338</v>
+        <v>78</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>78</v>
@@ -7266,13 +7343,13 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>78</v>
@@ -7295,14 +7372,12 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>78</v>
       </c>
@@ -7311,7 +7386,7 @@
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>78</v>
@@ -7323,22 +7398,22 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>169</v>
+        <v>226</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q52" s="2"/>
+      <c r="Q52" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="R52" t="s" s="2">
         <v>78</v>
       </c>
@@ -7358,11 +7433,13 @@
         <v>78</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="Y52" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z52" t="s" s="2">
-        <v>338</v>
+        <v>78</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>78</v>
@@ -7380,7 +7457,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7401,7 +7478,7 @@
         <v>78</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>78</v>
+        <v>193</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -7409,10 +7486,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7432,20 +7509,18 @@
         <v>78</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>282</v>
+        <v>230</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>342</v>
+        <v>231</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>344</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -7494,7 +7569,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>341</v>
+        <v>233</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7506,7 +7581,7 @@
         <v>78</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>78</v>
@@ -7515,7 +7590,7 @@
         <v>78</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -7523,14 +7598,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7546,25 +7621,25 @@
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>222</v>
+        <v>136</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>346</v>
+        <v>137</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q54" t="s" s="2">
-        <v>348</v>
-      </c>
+      <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
         <v>78</v>
       </c>
@@ -7608,7 +7683,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>345</v>
+        <v>237</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7620,7 +7695,7 @@
         <v>78</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>78</v>
@@ -7629,7 +7704,7 @@
         <v>78</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>189</v>
+        <v>234</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>78</v>
@@ -7637,42 +7712,46 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>78</v>
+        <v>239</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>226</v>
+        <v>136</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
       </c>
@@ -7720,19 +7799,19 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>78</v>
@@ -7741,7 +7820,7 @@
         <v>78</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>230</v>
+        <v>133</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -7749,21 +7828,21 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>78</v>
@@ -7772,20 +7851,18 @@
         <v>78</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>137</v>
+        <v>349</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -7810,13 +7887,13 @@
         <v>78</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>78</v>
+        <v>351</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>78</v>
+        <v>352</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>78</v>
@@ -7834,19 +7911,19 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>233</v>
+        <v>348</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>78</v>
@@ -7855,7 +7932,7 @@
         <v>78</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>230</v>
+        <v>78</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -7863,46 +7940,42 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>235</v>
+        <v>78</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>136</v>
+        <v>354</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>236</v>
+        <v>355</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>78</v>
       </c>
@@ -7950,19 +8023,19 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>238</v>
+        <v>353</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>78</v>
@@ -7971,7 +8044,7 @@
         <v>78</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -7979,10 +8052,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7990,10 +8063,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>78</v>
@@ -8002,16 +8075,16 @@
         <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>110</v>
+        <v>226</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8038,13 +8111,13 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>355</v>
+        <v>78</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>356</v>
+        <v>78</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -8062,13 +8135,13 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>78</v>
@@ -8091,10 +8164,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8102,7 +8175,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>90</v>
@@ -8114,16 +8187,16 @@
         <v>78</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>358</v>
+        <v>230</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>359</v>
+        <v>231</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>360</v>
+        <v>232</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8174,10 +8247,10 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>357</v>
+        <v>233</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>90</v>
@@ -8186,7 +8259,7 @@
         <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>78</v>
@@ -8195,7 +8268,7 @@
         <v>78</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -8210,7 +8283,7 @@
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8229,15 +8302,17 @@
         <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>362</v>
+        <v>137</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -8286,7 +8361,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>361</v>
+        <v>237</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8298,18 +8373,2510 @@
         <v>78</v>
       </c>
       <c r="AJ60" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="Y62" s="2"/>
+      <c r="Z62" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AK62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q64" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="R64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q70" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="R70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="Y72" s="2"/>
+      <c r="Z72" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="Y74" s="2"/>
+      <c r="Z74" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q76" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="R76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>78</v>
       </c>
     </row>

--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2971" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3115" uniqueCount="407">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T09:00:47+00:00</t>
+    <t>2025-05-22T16:12:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil FHIR pour les consentements lors de la préadmission</t>
+    <t>Profil Consent pour les consentements lors de la préadmission</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -580,14 +580,6 @@
     <t>A classification of the type of consents found in the statement. This element supports indexing and retrieval of consent statements.</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="59284-0"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
     <t>A classification of the type of consents found in a consent statement.</t>
   </si>
   <si>
@@ -604,6 +596,99 @@
   </si>
   <si>
     <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Consent.category.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Consent.category.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Consent.category.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/preadmission-consent-category-vs</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Consent.category.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Consent.patient</t>
@@ -743,29 +828,7 @@
     <t>Consent.policy.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Consent.policy.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Consent.policy.modifierExtension</t>
@@ -1000,10 +1063,6 @@
     <t>Consent.provision.securityLabel</t>
   </si>
   <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
     <t>Security Labels that define affected resources</t>
   </si>
   <si>
@@ -1194,7 +1253,7 @@
     <t>Consent.provision.provision.code</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/preadmission-consent-code-value-set</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/preadmission-consent-code-vs</t>
   </si>
   <si>
     <t>Consent.provision.provision.dataPeriod</t>
@@ -1528,7 +1587,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN82"/>
+  <dimension ref="A1:AN86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.015625" customWidth="true" bestFit="true"/>
@@ -1559,7 +1618,7 @@
     <col min="26" max="26" width="66.4609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1568,7 +1627,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="39.8203125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="25.59375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="39.890625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -3108,7 +3167,7 @@
         <v>78</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>78</v>
@@ -3126,10 +3185,10 @@
         <v>174</v>
       </c>
       <c r="Y14" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Z14" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>78</v>
@@ -3162,24 +3221,24 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>186</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3187,7 +3246,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>90</v>
@@ -3199,20 +3258,18 @@
         <v>78</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M15" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>191</v>
-      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>78</v>
@@ -3261,7 +3318,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3273,38 +3330,38 @@
         <v>78</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>192</v>
+        <v>78</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>78</v>
@@ -3313,19 +3370,19 @@
         <v>78</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>197</v>
+        <v>137</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>199</v>
+        <v>139</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3363,59 +3420,59 @@
         <v>78</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>78</v>
+        <v>195</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>78</v>
+        <v>196</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>201</v>
+        <v>78</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>203</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>205</v>
+        <v>78</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>80</v>
@@ -3430,18 +3487,20 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O17" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>78</v>
       </c>
@@ -3465,13 +3524,11 @@
         <v>78</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>78</v>
@@ -3489,7 +3546,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3504,35 +3561,35 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>210</v>
+        <v>78</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>214</v>
+        <v>78</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>78</v>
@@ -3544,16 +3601,20 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>215</v>
+        <v>187</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>78</v>
       </c>
@@ -3607,7 +3668,7 @@
         <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>78</v>
@@ -3616,24 +3677,24 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>210</v>
+        <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>78</v>
+        <v>214</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>78</v>
+        <v>215</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3641,7 +3702,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>90</v>
@@ -3656,16 +3717,16 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3715,7 +3776,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3730,24 +3791,24 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>78</v>
+        <v>221</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>224</v>
+        <v>78</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>78</v>
+        <v>222</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>78</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3755,10 +3816,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>78</v>
@@ -3767,18 +3828,20 @@
         <v>78</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -3827,13 +3890,13 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>78</v>
@@ -3842,35 +3905,35 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>78</v>
+        <v>229</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>78</v>
+        <v>230</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>78</v>
+        <v>231</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>78</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>78</v>
@@ -3879,18 +3942,20 @@
         <v>78</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>78</v>
@@ -3945,37 +4010,37 @@
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>78</v>
+        <v>239</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>78</v>
+        <v>240</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>78</v>
+        <v>241</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>135</v>
+        <v>243</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3991,20 +4056,18 @@
         <v>78</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>136</v>
+        <v>244</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>137</v>
+        <v>245</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -4053,7 +4116,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4065,63 +4128,61 @@
         <v>78</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>78</v>
+        <v>239</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>78</v>
+        <v>247</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>239</v>
+        <v>78</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>136</v>
+        <v>249</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>78</v>
       </c>
@@ -4169,28 +4230,28 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>78</v>
+        <v>253</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>78</v>
@@ -4198,10 +4259,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4212,7 +4273,7 @@
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>78</v>
@@ -4224,13 +4285,13 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>104</v>
+        <v>255</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4281,16 +4342,16 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>246</v>
+        <v>78</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>102</v>
@@ -4310,10 +4371,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4336,17 +4397,15 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>104</v>
+        <v>187</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>248</v>
+        <v>188</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -4395,7 +4454,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>247</v>
+        <v>190</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4404,10 +4463,10 @@
         <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>246</v>
+        <v>78</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>78</v>
@@ -4416,7 +4475,7 @@
         <v>78</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>78</v>
@@ -4424,21 +4483,21 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>78</v>
@@ -4447,23 +4506,21 @@
         <v>78</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>251</v>
+        <v>137</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>252</v>
+        <v>193</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>254</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>78</v>
       </c>
@@ -4487,13 +4544,13 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>255</v>
+        <v>78</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>256</v>
+        <v>78</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
@@ -4511,19 +4568,19 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>250</v>
+        <v>197</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>246</v>
+        <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
@@ -4532,7 +4589,7 @@
         <v>78</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>78</v>
@@ -4540,14 +4597,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>78</v>
+        <v>261</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4560,22 +4617,26 @@
         <v>78</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>226</v>
+        <v>136</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
       </c>
@@ -4623,7 +4684,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4635,7 +4696,7 @@
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>78</v>
@@ -4644,7 +4705,7 @@
         <v>78</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>78</v>
@@ -4652,10 +4713,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4678,13 +4739,13 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>230</v>
+        <v>104</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>231</v>
+        <v>266</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4735,7 +4796,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4744,10 +4805,10 @@
         <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>268</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>78</v>
@@ -4756,7 +4817,7 @@
         <v>78</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -4764,21 +4825,21 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>78</v>
@@ -4790,16 +4851,16 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>137</v>
+        <v>270</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>139</v>
+        <v>271</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4849,19 +4910,19 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>237</v>
+        <v>269</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>78</v>
+        <v>268</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>78</v>
@@ -4870,7 +4931,7 @@
         <v>78</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -4878,45 +4939,45 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>239</v>
+        <v>78</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>240</v>
+        <v>273</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>241</v>
+        <v>274</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>139</v>
+        <v>275</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>145</v>
+        <v>276</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -4941,13 +5002,13 @@
         <v>78</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>78</v>
+        <v>174</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>78</v>
+        <v>277</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>78</v>
+        <v>278</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>78</v>
@@ -4965,19 +5026,19 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>78</v>
+        <v>268</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>78</v>
@@ -4986,7 +5047,7 @@
         <v>78</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -4994,10 +5055,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5005,10 +5066,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>78</v>
@@ -5020,13 +5081,13 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5077,13 +5138,13 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>78</v>
@@ -5106,10 +5167,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5132,13 +5193,13 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>268</v>
+        <v>187</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>269</v>
+        <v>188</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>270</v>
+        <v>189</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5189,7 +5250,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>267</v>
+        <v>190</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5201,7 +5262,7 @@
         <v>78</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>78</v>
@@ -5210,7 +5271,7 @@
         <v>78</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>78</v>
@@ -5218,21 +5279,21 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>78</v>
@@ -5244,15 +5305,17 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>272</v>
+        <v>137</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5301,19 +5364,19 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>271</v>
+        <v>197</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>78</v>
@@ -5322,7 +5385,7 @@
         <v>78</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>78</v>
@@ -5330,42 +5393,46 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>78</v>
+        <v>261</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>226</v>
+        <v>136</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
       </c>
@@ -5413,19 +5480,19 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>78</v>
@@ -5434,7 +5501,7 @@
         <v>78</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
@@ -5442,10 +5509,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5453,7 +5520,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>90</v>
@@ -5465,16 +5532,16 @@
         <v>78</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>230</v>
+        <v>286</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>231</v>
+        <v>287</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>232</v>
+        <v>288</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5525,10 +5592,10 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>233</v>
+        <v>285</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>90</v>
@@ -5537,7 +5604,7 @@
         <v>78</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>78</v>
@@ -5546,7 +5613,7 @@
         <v>78</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
@@ -5554,21 +5621,21 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>78</v>
@@ -5580,17 +5647,15 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>136</v>
+        <v>290</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>137</v>
+        <v>291</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -5639,19 +5704,19 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>237</v>
+        <v>289</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>78</v>
@@ -5660,7 +5725,7 @@
         <v>78</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -5668,46 +5733,42 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>239</v>
+        <v>78</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>136</v>
+        <v>225</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>240</v>
+        <v>294</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>78</v>
       </c>
@@ -5755,19 +5816,19 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>242</v>
+        <v>293</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>78</v>
@@ -5776,7 +5837,7 @@
         <v>78</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -5784,10 +5845,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5810,13 +5871,13 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>110</v>
+        <v>255</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5843,11 +5904,13 @@
         <v>78</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z38" t="s" s="2">
-        <v>283</v>
+        <v>78</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>78</v>
@@ -5865,7 +5928,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5894,10 +5957,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5917,16 +5980,16 @@
         <v>78</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>285</v>
+        <v>187</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>286</v>
+        <v>188</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>287</v>
+        <v>189</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5977,7 +6040,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>284</v>
+        <v>190</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -5989,7 +6052,7 @@
         <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>78</v>
@@ -5998,7 +6061,7 @@
         <v>78</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
@@ -6006,14 +6069,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6032,22 +6095,22 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>226</v>
+        <v>136</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>289</v>
+        <v>137</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q40" t="s" s="2">
-        <v>291</v>
-      </c>
+      <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
         <v>78</v>
       </c>
@@ -6091,7 +6154,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>288</v>
+        <v>197</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6103,7 +6166,7 @@
         <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>78</v>
@@ -6112,7 +6175,7 @@
         <v>78</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -6120,42 +6183,46 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>78</v>
+        <v>261</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>230</v>
+        <v>136</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>231</v>
+        <v>262</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>78</v>
       </c>
@@ -6203,19 +6270,19 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>78</v>
@@ -6224,7 +6291,7 @@
         <v>78</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>234</v>
+        <v>133</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>78</v>
@@ -6232,21 +6299,21 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>78</v>
@@ -6255,20 +6322,18 @@
         <v>78</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>137</v>
+        <v>303</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -6293,13 +6358,11 @@
         <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>78</v>
+        <v>305</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
@@ -6317,19 +6380,19 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>237</v>
+        <v>302</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>78</v>
@@ -6338,7 +6401,7 @@
         <v>78</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>78</v>
@@ -6346,46 +6409,42 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>239</v>
+        <v>78</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>136</v>
+        <v>307</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>240</v>
+        <v>308</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>78</v>
       </c>
@@ -6433,19 +6492,19 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>242</v>
+        <v>306</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>78</v>
@@ -6454,7 +6513,7 @@
         <v>78</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
@@ -6462,10 +6521,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6473,10 +6532,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>78</v>
@@ -6488,20 +6547,22 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>170</v>
+        <v>255</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q44" s="2"/>
+      <c r="Q44" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="R44" t="s" s="2">
         <v>78</v>
       </c>
@@ -6521,13 +6582,13 @@
         <v>78</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>298</v>
+        <v>78</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>299</v>
+        <v>78</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -6545,13 +6606,13 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>78</v>
@@ -6574,10 +6635,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6585,7 +6646,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>90</v>
@@ -6600,13 +6661,13 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>301</v>
+        <v>187</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>302</v>
+        <v>188</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>303</v>
+        <v>189</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6657,10 +6718,10 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>90</v>
@@ -6669,7 +6730,7 @@
         <v>78</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>78</v>
@@ -6678,7 +6739,7 @@
         <v>78</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>78</v>
@@ -6686,14 +6747,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6709,27 +6770,25 @@
         <v>78</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>305</v>
+        <v>137</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>306</v>
+        <v>193</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>307</v>
+        <v>139</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q46" t="s" s="2">
-        <v>308</v>
-      </c>
+      <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
         <v>78</v>
       </c>
@@ -6749,13 +6808,13 @@
         <v>78</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>309</v>
+        <v>78</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>310</v>
+        <v>78</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>311</v>
+        <v>78</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>78</v>
@@ -6773,7 +6832,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>304</v>
+        <v>197</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6785,7 +6844,7 @@
         <v>78</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>78</v>
@@ -6794,7 +6853,7 @@
         <v>78</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -6802,14 +6861,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>78</v>
+        <v>261</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6822,24 +6881,26 @@
         <v>78</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>313</v>
+        <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>314</v>
+        <v>262</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>315</v>
+        <v>263</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>78</v>
       </c>
@@ -6863,13 +6924,13 @@
         <v>78</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>317</v>
+        <v>78</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>318</v>
+        <v>78</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>78</v>
@@ -6887,7 +6948,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>312</v>
+        <v>264</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -6899,7 +6960,7 @@
         <v>78</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>78</v>
@@ -6908,7 +6969,7 @@
         <v>78</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>
@@ -6916,10 +6977,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6927,10 +6988,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>78</v>
@@ -6939,20 +7000,18 @@
         <v>78</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>313</v>
+        <v>170</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -6980,10 +7039,10 @@
         <v>174</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>78</v>
@@ -7001,13 +7060,13 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>78</v>
@@ -7030,10 +7089,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7041,10 +7100,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>78</v>
@@ -7053,20 +7112,18 @@
         <v>78</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7091,13 +7148,13 @@
         <v>78</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>329</v>
+        <v>78</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>330</v>
+        <v>78</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>78</v>
@@ -7115,13 +7172,13 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>78</v>
@@ -7144,10 +7201,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7173,19 +7230,21 @@
         <v>170</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q50" s="2"/>
+      <c r="Q50" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="R50" t="s" s="2">
         <v>78</v>
       </c>
@@ -7205,13 +7264,13 @@
         <v>78</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>78</v>
@@ -7229,7 +7288,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7258,10 +7317,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7272,7 +7331,7 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>78</v>
@@ -7284,16 +7343,16 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>285</v>
+        <v>199</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7319,13 +7378,13 @@
         <v>78</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>78</v>
+        <v>174</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>78</v>
+        <v>338</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>78</v>
+        <v>339</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>78</v>
@@ -7343,13 +7402,13 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>78</v>
@@ -7372,10 +7431,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7398,48 +7457,48 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q52" t="s" s="2">
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y52" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="R52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="Z52" t="s" s="2">
-        <v>78</v>
+        <v>345</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>78</v>
@@ -7457,7 +7516,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7478,7 +7537,7 @@
         <v>78</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>193</v>
+        <v>78</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -7486,10 +7545,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7500,7 +7559,7 @@
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>78</v>
@@ -7509,18 +7568,20 @@
         <v>78</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>230</v>
+        <v>199</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>231</v>
+        <v>347</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -7545,13 +7606,13 @@
         <v>78</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>78</v>
+        <v>174</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>78</v>
+        <v>350</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>78</v>
+        <v>351</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
@@ -7569,19 +7630,19 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>233</v>
+        <v>346</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>78</v>
@@ -7590,7 +7651,7 @@
         <v>78</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -7598,14 +7659,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7621,19 +7682,19 @@
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>137</v>
+        <v>353</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>236</v>
+        <v>354</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>139</v>
+        <v>355</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7659,13 +7720,13 @@
         <v>78</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>78</v>
+        <v>331</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>78</v>
+        <v>356</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>78</v>
+        <v>357</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -7683,7 +7744,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>237</v>
+        <v>352</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7695,7 +7756,7 @@
         <v>78</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>78</v>
@@ -7704,7 +7765,7 @@
         <v>78</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>78</v>
@@ -7712,46 +7773,44 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>239</v>
+        <v>78</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>136</v>
+        <v>307</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>240</v>
+        <v>359</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>241</v>
+        <v>360</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>78</v>
       </c>
@@ -7799,19 +7858,19 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>242</v>
+        <v>358</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>78</v>
@@ -7820,7 +7879,7 @@
         <v>78</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -7828,10 +7887,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7839,10 +7898,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>78</v>
@@ -7854,20 +7913,22 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>110</v>
+        <v>255</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q56" s="2"/>
+      <c r="Q56" t="s" s="2">
+        <v>365</v>
+      </c>
       <c r="R56" t="s" s="2">
         <v>78</v>
       </c>
@@ -7887,13 +7948,13 @@
         <v>78</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>351</v>
+        <v>78</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>352</v>
+        <v>78</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>78</v>
@@ -7911,13 +7972,13 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>78</v>
@@ -7932,7 +7993,7 @@
         <v>78</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>78</v>
+        <v>222</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -7940,10 +8001,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7951,7 +8012,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>90</v>
@@ -7963,16 +8024,16 @@
         <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>354</v>
+        <v>187</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>355</v>
+        <v>188</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>356</v>
+        <v>189</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8023,10 +8084,10 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>353</v>
+        <v>190</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>90</v>
@@ -8035,7 +8096,7 @@
         <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>78</v>
@@ -8044,7 +8105,7 @@
         <v>78</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -8052,14 +8113,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8078,15 +8139,17 @@
         <v>78</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>226</v>
+        <v>136</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>358</v>
+        <v>137</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -8135,7 +8198,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>357</v>
+        <v>197</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8147,7 +8210,7 @@
         <v>78</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>78</v>
@@ -8156,7 +8219,7 @@
         <v>78</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -8164,42 +8227,46 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>78</v>
+        <v>261</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>230</v>
+        <v>136</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>231</v>
+        <v>262</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
       </c>
@@ -8247,19 +8314,19 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>78</v>
@@ -8268,7 +8335,7 @@
         <v>78</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>234</v>
+        <v>133</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -8276,21 +8343,21 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -8299,20 +8366,18 @@
         <v>78</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>137</v>
+        <v>370</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -8337,13 +8402,13 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>78</v>
+        <v>372</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>78</v>
+        <v>373</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -8361,19 +8426,19 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>237</v>
+        <v>369</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>78</v>
@@ -8382,7 +8447,7 @@
         <v>78</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -8390,46 +8455,42 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>239</v>
+        <v>78</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J61" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>136</v>
+        <v>375</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>240</v>
+        <v>376</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>78</v>
       </c>
@@ -8477,19 +8538,19 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>242</v>
+        <v>374</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>78</v>
@@ -8498,7 +8559,7 @@
         <v>78</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>78</v>
@@ -8506,10 +8567,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8520,7 +8581,7 @@
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
@@ -8529,16 +8590,16 @@
         <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>110</v>
+        <v>255</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>281</v>
+        <v>379</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>282</v>
+        <v>380</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8565,11 +8626,13 @@
         <v>78</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="Y62" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z62" t="s" s="2">
-        <v>283</v>
+        <v>78</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>78</v>
@@ -8587,13 +8650,13 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>280</v>
+        <v>378</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>78</v>
@@ -8616,10 +8679,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8639,16 +8702,16 @@
         <v>78</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>285</v>
+        <v>187</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>286</v>
+        <v>188</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>287</v>
+        <v>189</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8699,7 +8762,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>284</v>
+        <v>190</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -8711,7 +8774,7 @@
         <v>78</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>78</v>
@@ -8720,7 +8783,7 @@
         <v>78</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -8728,14 +8791,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8754,22 +8817,22 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>226</v>
+        <v>136</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>289</v>
+        <v>137</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q64" t="s" s="2">
-        <v>291</v>
-      </c>
+      <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
         <v>78</v>
       </c>
@@ -8813,7 +8876,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>288</v>
+        <v>197</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -8825,7 +8888,7 @@
         <v>78</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>78</v>
@@ -8834,7 +8897,7 @@
         <v>78</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -8842,42 +8905,46 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>78</v>
+        <v>261</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>230</v>
+        <v>136</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>231</v>
+        <v>262</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
       </c>
@@ -8925,19 +8992,19 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>78</v>
@@ -8946,7 +9013,7 @@
         <v>78</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>234</v>
+        <v>133</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
@@ -8954,21 +9021,21 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>78</v>
@@ -8977,20 +9044,18 @@
         <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>137</v>
+        <v>303</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9015,13 +9080,11 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>78</v>
+        <v>305</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -9039,19 +9102,19 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>237</v>
+        <v>302</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
@@ -9060,7 +9123,7 @@
         <v>78</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>78</v>
@@ -9068,46 +9131,42 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>239</v>
+        <v>78</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>136</v>
+        <v>307</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>240</v>
+        <v>308</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>78</v>
       </c>
@@ -9155,19 +9214,19 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>242</v>
+        <v>306</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>78</v>
@@ -9176,7 +9235,7 @@
         <v>78</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>78</v>
@@ -9184,10 +9243,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9195,10 +9254,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>78</v>
@@ -9210,20 +9269,22 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>170</v>
+        <v>255</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q68" s="2"/>
+      <c r="Q68" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="R68" t="s" s="2">
         <v>78</v>
       </c>
@@ -9243,13 +9304,13 @@
         <v>78</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>298</v>
+        <v>78</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>299</v>
+        <v>78</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>78</v>
@@ -9267,13 +9328,13 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>78</v>
@@ -9296,10 +9357,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9307,7 +9368,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>90</v>
@@ -9322,13 +9383,13 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>301</v>
+        <v>187</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>302</v>
+        <v>188</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>303</v>
+        <v>189</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9379,10 +9440,10 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>90</v>
@@ -9391,7 +9452,7 @@
         <v>78</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>78</v>
@@ -9400,7 +9461,7 @@
         <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>78</v>
@@ -9408,14 +9469,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -9431,27 +9492,25 @@
         <v>78</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>305</v>
+        <v>137</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>306</v>
+        <v>193</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>307</v>
+        <v>139</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q70" t="s" s="2">
-        <v>308</v>
-      </c>
+      <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
         <v>78</v>
       </c>
@@ -9471,13 +9530,13 @@
         <v>78</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>309</v>
+        <v>78</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>310</v>
+        <v>78</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>311</v>
+        <v>78</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>78</v>
@@ -9495,7 +9554,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>304</v>
+        <v>197</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -9507,7 +9566,7 @@
         <v>78</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>78</v>
@@ -9516,7 +9575,7 @@
         <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>78</v>
@@ -9524,14 +9583,14 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>78</v>
+        <v>261</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -9544,24 +9603,26 @@
         <v>78</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J71" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>313</v>
+        <v>136</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>314</v>
+        <v>262</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>315</v>
+        <v>263</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
       </c>
@@ -9585,13 +9646,13 @@
         <v>78</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>317</v>
+        <v>78</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>318</v>
+        <v>78</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
@@ -9609,7 +9670,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>312</v>
+        <v>264</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -9621,7 +9682,7 @@
         <v>78</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>78</v>
@@ -9630,7 +9691,7 @@
         <v>78</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>78</v>
@@ -9638,10 +9699,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9661,20 +9722,18 @@
         <v>78</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>313</v>
+        <v>170</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -9699,11 +9758,13 @@
         <v>78</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="Y72" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="Z72" t="s" s="2">
-        <v>374</v>
+        <v>321</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>78</v>
@@ -9721,13 +9782,13 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>78</v>
@@ -9750,10 +9811,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9761,10 +9822,10 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>78</v>
@@ -9773,20 +9834,18 @@
         <v>78</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>78</v>
@@ -9811,13 +9870,13 @@
         <v>78</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>329</v>
+        <v>78</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>330</v>
+        <v>78</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>78</v>
@@ -9835,13 +9894,13 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>78</v>
@@ -9864,10 +9923,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9875,10 +9934,10 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>78</v>
@@ -9893,19 +9952,21 @@
         <v>170</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q74" s="2"/>
+      <c r="Q74" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="R74" t="s" s="2">
         <v>78</v>
       </c>
@@ -9925,11 +9986,13 @@
         <v>78</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="Y74" s="2"/>
+        <v>331</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="Z74" t="s" s="2">
-        <v>377</v>
+        <v>333</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>78</v>
@@ -9947,7 +10010,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -9976,10 +10039,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>378</v>
+        <v>393</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>378</v>
+        <v>393</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9990,7 +10053,7 @@
         <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>78</v>
@@ -10002,16 +10065,16 @@
         <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>285</v>
+        <v>199</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10037,13 +10100,13 @@
         <v>78</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>78</v>
+        <v>174</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>78</v>
+        <v>338</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>78</v>
+        <v>339</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>78</v>
@@ -10061,13 +10124,13 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>78</v>
@@ -10090,10 +10153,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10101,10 +10164,10 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>78</v>
@@ -10116,22 +10179,22 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q76" t="s" s="2">
-        <v>344</v>
-      </c>
+      <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
         <v>78</v>
       </c>
@@ -10151,13 +10214,11 @@
         <v>78</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>78</v>
+        <v>395</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>78</v>
@@ -10175,7 +10236,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10196,7 +10257,7 @@
         <v>78</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>193</v>
+        <v>78</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>78</v>
@@ -10204,10 +10265,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10218,7 +10279,7 @@
         <v>79</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>78</v>
@@ -10227,18 +10288,20 @@
         <v>78</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>230</v>
+        <v>199</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>231</v>
+        <v>347</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>78</v>
@@ -10263,13 +10326,13 @@
         <v>78</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>78</v>
+        <v>174</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>78</v>
+        <v>350</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>78</v>
+        <v>351</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>78</v>
@@ -10287,19 +10350,19 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>233</v>
+        <v>346</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>78</v>
@@ -10308,7 +10371,7 @@
         <v>78</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -10316,21 +10379,21 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>78</v>
@@ -10339,19 +10402,19 @@
         <v>78</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>137</v>
+        <v>353</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>236</v>
+        <v>354</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>139</v>
+        <v>355</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10377,13 +10440,11 @@
         <v>78</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>78</v>
+        <v>398</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>78</v>
@@ -10401,7 +10462,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>237</v>
+        <v>352</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -10413,7 +10474,7 @@
         <v>78</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>78</v>
@@ -10422,7 +10483,7 @@
         <v>78</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -10430,46 +10491,44 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>239</v>
+        <v>78</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J79" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>136</v>
+        <v>307</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>240</v>
+        <v>359</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>241</v>
+        <v>360</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>78</v>
       </c>
@@ -10517,19 +10576,19 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>242</v>
+        <v>358</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>78</v>
@@ -10538,7 +10597,7 @@
         <v>78</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -10546,10 +10605,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10557,10 +10616,10 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>78</v>
@@ -10572,20 +10631,22 @@
         <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>110</v>
+        <v>255</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q80" s="2"/>
+      <c r="Q80" t="s" s="2">
+        <v>365</v>
+      </c>
       <c r="R80" t="s" s="2">
         <v>78</v>
       </c>
@@ -10605,13 +10666,13 @@
         <v>78</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>351</v>
+        <v>78</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>352</v>
+        <v>78</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>78</v>
@@ -10629,13 +10690,13 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>78</v>
@@ -10650,7 +10711,7 @@
         <v>78</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>78</v>
+        <v>222</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -10658,10 +10719,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>384</v>
+        <v>401</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>384</v>
+        <v>401</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10669,7 +10730,7 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>90</v>
@@ -10681,16 +10742,16 @@
         <v>78</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>354</v>
+        <v>187</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>355</v>
+        <v>188</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>356</v>
+        <v>189</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10741,10 +10802,10 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>353</v>
+        <v>190</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>90</v>
@@ -10753,7 +10814,7 @@
         <v>78</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>78</v>
@@ -10762,7 +10823,7 @@
         <v>78</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
@@ -10770,14 +10831,14 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -10796,15 +10857,17 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>358</v>
+        <v>137</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>78</v>
@@ -10853,7 +10916,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>357</v>
+        <v>197</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -10865,18 +10928,470 @@
         <v>78</v>
       </c>
       <c r="AJ82" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN82" t="s" s="2">
+      <c r="AK84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>78</v>
       </c>
     </row>

--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T16:12:30+00:00</t>
+    <t>2025-05-26T06:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-26T06:59:47+00:00</t>
+    <t>2025-06-02T15:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T15:02:23+00:00</t>
+    <t>2025-10-22T09:09:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-22T09:09:51+00:00</t>
+    <t>2025-10-28T10:00:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T10:00:18+00:00</t>
+    <t>2025-11-19T09:47:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-19T09:47:12+00:00</t>
+    <t>2026-01-14T12:51:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T12:51:21+00:00</t>
+    <t>2026-02-24T09:27:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3115" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3115" uniqueCount="406">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T09:27:09+00:00</t>
+    <t>2026-04-10T11:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -515,9 +515,6 @@
   </si>
   <si>
     <t>The Consent Directive that is pointed to might be in various lifecycle states, e.g., a revoked Consent Directive.</t>
-  </si>
-  <si>
-    <t>active</t>
   </si>
   <si>
     <t>required</t>
@@ -2940,31 +2937,31 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X12" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="S12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X12" t="s" s="2">
+      <c r="Y12" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="Z12" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>78</v>
@@ -2997,24 +2994,24 @@
         <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AM12" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AM12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>168</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3037,13 +3034,13 @@
         <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3055,29 +3052,29 @@
         <v>78</v>
       </c>
       <c r="S13" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X13" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="T13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X13" t="s" s="2">
+      <c r="Y13" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="Z13" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="Z13" t="s" s="2">
-        <v>176</v>
-      </c>
       <c r="AA13" t="s" s="2">
         <v>78</v>
       </c>
@@ -3094,7 +3091,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>90</v>
@@ -3123,10 +3120,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3149,13 +3146,13 @@
         <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3182,14 +3179,14 @@
         <v>78</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Y14" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="Z14" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="Z14" t="s" s="2">
-        <v>181</v>
-      </c>
       <c r="AA14" t="s" s="2">
         <v>78</v>
       </c>
@@ -3206,7 +3203,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>90</v>
@@ -3221,24 +3218,24 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>185</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3261,13 +3258,13 @@
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3318,7 +3315,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3339,7 +3336,7 @@
         <v>78</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>78</v>
@@ -3347,10 +3344,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3379,7 +3376,7 @@
         <v>137</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>139</v>
@@ -3420,19 +3417,19 @@
         <v>78</v>
       </c>
       <c r="AB16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AC16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AC16" t="s" s="2">
+      <c r="AD16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE16" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AD16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE16" t="s" s="2">
+      <c r="AF16" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3453,7 +3450,7 @@
         <v>78</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>78</v>
@@ -3461,10 +3458,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3487,19 +3484,19 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>78</v>
@@ -3524,29 +3521,29 @@
         <v>78</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3564,10 +3561,10 @@
         <v>78</v>
       </c>
       <c r="AL17" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>78</v>
@@ -3575,10 +3572,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3601,19 +3598,19 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -3662,7 +3659,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3680,10 +3677,10 @@
         <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>78</v>
@@ -3691,10 +3688,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3717,16 +3714,16 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3776,7 +3773,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3791,24 +3788,24 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AL19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>223</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3831,16 +3828,16 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3890,7 +3887,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3905,28 +3902,28 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AM20" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>232</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3945,16 +3942,16 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4004,7 +4001,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4019,28 +4016,28 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="AL21" t="s" s="2">
+      <c r="AM21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>241</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4059,13 +4056,13 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4116,7 +4113,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4131,7 +4128,7 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>78</v>
@@ -4140,15 +4137,15 @@
         <v>78</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4171,16 +4168,16 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4230,7 +4227,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4248,7 +4245,7 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>78</v>
@@ -4259,10 +4256,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4285,13 +4282,13 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4342,7 +4339,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4371,10 +4368,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4397,13 +4394,13 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4454,7 +4451,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4475,7 +4472,7 @@
         <v>78</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>78</v>
@@ -4483,10 +4480,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4515,7 +4512,7 @@
         <v>137</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N26" t="s" s="2">
         <v>139</v>
@@ -4568,7 +4565,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4589,7 +4586,7 @@
         <v>78</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>78</v>
@@ -4597,14 +4594,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4626,10 +4623,10 @@
         <v>136</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>139</v>
@@ -4684,7 +4681,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4713,10 +4710,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4742,10 +4739,10 @@
         <v>104</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4796,7 +4793,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4805,7 +4802,7 @@
         <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>102</v>
@@ -4825,10 +4822,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4854,13 +4851,13 @@
         <v>104</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4910,7 +4907,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4919,7 +4916,7 @@
         <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>102</v>
@@ -4939,10 +4936,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4965,19 +4962,19 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -5002,14 +4999,14 @@
         <v>78</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Y30" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="Z30" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="Z30" t="s" s="2">
-        <v>278</v>
-      </c>
       <c r="AA30" t="s" s="2">
         <v>78</v>
       </c>
@@ -5026,7 +5023,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5035,7 +5032,7 @@
         <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>102</v>
@@ -5055,10 +5052,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5081,13 +5078,13 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5138,7 +5135,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5167,10 +5164,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5193,13 +5190,13 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5250,7 +5247,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5271,7 +5268,7 @@
         <v>78</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>78</v>
@@ -5279,10 +5276,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5311,7 +5308,7 @@
         <v>137</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>139</v>
@@ -5364,7 +5361,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5385,7 +5382,7 @@
         <v>78</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>78</v>
@@ -5393,14 +5390,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5422,10 +5419,10 @@
         <v>136</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>139</v>
@@ -5480,7 +5477,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5509,10 +5506,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5535,13 +5532,13 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5592,7 +5589,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>90</v>
@@ -5621,10 +5618,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5647,13 +5644,13 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5704,7 +5701,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5733,10 +5730,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5759,13 +5756,13 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5816,7 +5813,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5845,10 +5842,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5871,13 +5868,13 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5928,7 +5925,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5957,10 +5954,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5983,13 +5980,13 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6040,7 +6037,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6061,7 +6058,7 @@
         <v>78</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
@@ -6069,10 +6066,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6101,7 +6098,7 @@
         <v>137</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>139</v>
@@ -6154,7 +6151,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6175,7 +6172,7 @@
         <v>78</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -6183,14 +6180,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6212,10 +6209,10 @@
         <v>136</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>139</v>
@@ -6270,7 +6267,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6299,10 +6296,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6328,10 +6325,10 @@
         <v>110</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6358,11 +6355,11 @@
         <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
@@ -6380,7 +6377,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6409,10 +6406,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6435,13 +6432,13 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6492,7 +6489,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6521,10 +6518,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6547,13 +6544,13 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6561,7 +6558,7 @@
         <v>78</v>
       </c>
       <c r="Q44" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R44" t="s" s="2">
         <v>78</v>
@@ -6606,7 +6603,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6635,10 +6632,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6661,13 +6658,13 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6718,7 +6715,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6739,7 +6736,7 @@
         <v>78</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>78</v>
@@ -6747,10 +6744,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6779,7 +6776,7 @@
         <v>137</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>139</v>
@@ -6832,7 +6829,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6853,7 +6850,7 @@
         <v>78</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -6861,14 +6858,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6890,10 +6887,10 @@
         <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>139</v>
@@ -6948,7 +6945,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -6977,10 +6974,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7003,13 +7000,13 @@
         <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7036,14 +7033,14 @@
         <v>78</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>321</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>78</v>
       </c>
@@ -7060,7 +7057,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>90</v>
@@ -7089,10 +7086,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7115,13 +7112,13 @@
         <v>78</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7172,7 +7169,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>90</v>
@@ -7201,10 +7198,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7227,51 +7224,51 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q50" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="R50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X50" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="R50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X50" t="s" s="2">
+      <c r="Y50" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="Y50" t="s" s="2">
+      <c r="Z50" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>333</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>78</v>
       </c>
@@ -7288,7 +7285,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7317,10 +7314,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7343,16 +7340,16 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7378,14 +7375,14 @@
         <v>78</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="Z51" t="s" s="2">
-        <v>339</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>78</v>
       </c>
@@ -7402,7 +7399,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7431,10 +7428,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7457,16 +7454,16 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7492,14 +7489,14 @@
         <v>78</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="Z52" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>78</v>
       </c>
@@ -7516,7 +7513,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7545,10 +7542,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7571,16 +7568,16 @@
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7606,14 +7603,14 @@
         <v>78</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Y53" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="Z53" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="Z53" t="s" s="2">
-        <v>351</v>
-      </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
       </c>
@@ -7630,7 +7627,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7659,10 +7656,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7685,16 +7682,16 @@
         <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7720,14 +7717,14 @@
         <v>78</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Y54" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="Z54" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="Z54" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
       </c>
@@ -7744,7 +7741,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7773,10 +7770,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7799,16 +7796,16 @@
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7858,7 +7855,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -7887,10 +7884,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7913,13 +7910,13 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7927,7 +7924,7 @@
         <v>78</v>
       </c>
       <c r="Q56" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="R56" t="s" s="2">
         <v>78</v>
@@ -7972,7 +7969,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -7993,7 +7990,7 @@
         <v>78</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -8001,10 +7998,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8027,13 +8024,13 @@
         <v>78</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8084,7 +8081,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8105,7 +8102,7 @@
         <v>78</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -8113,10 +8110,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8145,7 +8142,7 @@
         <v>137</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>139</v>
@@ -8198,7 +8195,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8219,7 +8216,7 @@
         <v>78</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -8227,14 +8224,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8256,10 +8253,10 @@
         <v>136</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>139</v>
@@ -8314,7 +8311,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8343,10 +8340,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8372,10 +8369,10 @@
         <v>110</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8402,14 +8399,14 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
       </c>
@@ -8426,7 +8423,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>90</v>
@@ -8455,10 +8452,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8481,13 +8478,13 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8538,7 +8535,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>90</v>
@@ -8567,10 +8564,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8593,13 +8590,13 @@
         <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8650,7 +8647,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -8679,10 +8676,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8705,13 +8702,13 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8762,7 +8759,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -8783,7 +8780,7 @@
         <v>78</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -8791,10 +8788,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8823,7 +8820,7 @@
         <v>137</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>139</v>
@@ -8876,7 +8873,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -8897,7 +8894,7 @@
         <v>78</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -8905,14 +8902,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8934,10 +8931,10 @@
         <v>136</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>139</v>
@@ -8992,7 +8989,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9021,10 +9018,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9050,10 +9047,10 @@
         <v>110</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9080,11 +9077,11 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -9102,7 +9099,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9131,10 +9128,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9157,13 +9154,13 @@
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9214,7 +9211,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9243,10 +9240,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9269,13 +9266,13 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9283,7 +9280,7 @@
         <v>78</v>
       </c>
       <c r="Q68" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R68" t="s" s="2">
         <v>78</v>
@@ -9328,7 +9325,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9357,10 +9354,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9383,13 +9380,13 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9440,7 +9437,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9461,7 +9458,7 @@
         <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>78</v>
@@ -9469,10 +9466,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9501,7 +9498,7 @@
         <v>137</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>139</v>
@@ -9554,7 +9551,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -9575,7 +9572,7 @@
         <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>78</v>
@@ -9583,14 +9580,14 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -9612,10 +9609,10 @@
         <v>136</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>139</v>
@@ -9670,7 +9667,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -9699,10 +9696,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9725,13 +9722,13 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9758,14 +9755,14 @@
         <v>78</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="Z72" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="Z72" t="s" s="2">
-        <v>321</v>
-      </c>
       <c r="AA72" t="s" s="2">
         <v>78</v>
       </c>
@@ -9782,7 +9779,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>90</v>
@@ -9811,10 +9808,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9837,13 +9834,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9894,7 +9891,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>90</v>
@@ -9923,10 +9920,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9949,51 +9946,51 @@
         <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q74" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="R74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X74" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="R74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X74" t="s" s="2">
+      <c r="Y74" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="Y74" t="s" s="2">
+      <c r="Z74" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="Z74" t="s" s="2">
-        <v>333</v>
-      </c>
       <c r="AA74" t="s" s="2">
         <v>78</v>
       </c>
@@ -10010,7 +10007,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10039,10 +10036,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10065,16 +10062,16 @@
         <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10100,14 +10097,14 @@
         <v>78</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="Z75" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="Z75" t="s" s="2">
-        <v>339</v>
-      </c>
       <c r="AA75" t="s" s="2">
         <v>78</v>
       </c>
@@ -10124,7 +10121,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10153,10 +10150,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10179,16 +10176,16 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10214,11 +10211,11 @@
         <v>78</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>78</v>
@@ -10236,7 +10233,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10265,10 +10262,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10291,16 +10288,16 @@
         <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10326,14 +10323,14 @@
         <v>78</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Y77" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="Z77" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="Z77" t="s" s="2">
-        <v>351</v>
-      </c>
       <c r="AA77" t="s" s="2">
         <v>78</v>
       </c>
@@ -10350,7 +10347,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10379,10 +10376,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10405,16 +10402,16 @@
         <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10440,11 +10437,11 @@
         <v>78</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>78</v>
@@ -10462,7 +10459,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -10491,10 +10488,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10517,16 +10514,16 @@
         <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10576,7 +10573,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -10605,10 +10602,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10631,13 +10628,13 @@
         <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -10645,7 +10642,7 @@
         <v>78</v>
       </c>
       <c r="Q80" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="R80" t="s" s="2">
         <v>78</v>
@@ -10690,7 +10687,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -10711,7 +10708,7 @@
         <v>78</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -10719,10 +10716,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10745,13 +10742,13 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10802,7 +10799,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -10823,7 +10820,7 @@
         <v>78</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
@@ -10831,10 +10828,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10863,7 +10860,7 @@
         <v>137</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>139</v>
@@ -10916,7 +10913,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -10937,7 +10934,7 @@
         <v>78</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
@@ -10945,14 +10942,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -10974,10 +10971,10 @@
         <v>136</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>139</v>
@@ -11032,7 +11029,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11061,10 +11058,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11090,10 +11087,10 @@
         <v>110</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11120,14 +11117,14 @@
         <v>78</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Y84" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="Z84" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="Z84" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AA84" t="s" s="2">
         <v>78</v>
       </c>
@@ -11144,7 +11141,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>90</v>
@@ -11173,10 +11170,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11199,13 +11196,13 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11256,7 +11253,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>90</v>
@@ -11285,10 +11282,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11314,10 +11311,10 @@
         <v>81</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11368,7 +11365,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
